--- a/classifier/data/dataset_summary.xlsx
+++ b/classifier/data/dataset_summary.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_counts" sheetId="1" r:id="Re98703b0eae2453f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="label_counts" sheetId="2" r:id="R837100890509475a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="split_counts" sheetId="3" r:id="R7f6de87342184276"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="split_by_label" sheetId="4" r:id="R2c839c0fe1a04d30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_counts" sheetId="1" r:id="Rc3295a76f45f4e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="label_counts" sheetId="2" r:id="Ra1c24eef9e754919"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="split_counts" sheetId="3" r:id="Rc575ef4f5fa544e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="split_by_label" sheetId="4" r:id="R238d7d3e14f741d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -426,7 +426,7 @@
         <x:v>separable_train.xlsx</x:v>
       </x:c>
       <x:c r="C3" t="n">
-        <x:v>249</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -506,7 +506,7 @@
         <x:v>separable</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>259</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -539,7 +539,7 @@
         <x:v>train</x:v>
       </x:c>
       <x:c r="B2" t="n">
-        <x:v>582</x:v>
+        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -547,7 +547,7 @@
         <x:v>valid</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -585,7 +585,7 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="C2" t="n">
-        <x:v>233</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="D2" t="n">
         <x:v>159</x:v>
@@ -599,7 +599,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C3" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D3" t="n">
         <x:v>18</x:v>
